--- a/Toronto_Bikeshare_Stations.xlsx
+++ b/Toronto_Bikeshare_Stations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ENVSOCTY4GA3\Applied-Spatial-Statistics\Bikeshare_Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\toronto cycling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E1F4F1-7A9B-49B0-946E-8F8CE0C238FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79A9428B-00EF-43C0-A44E-FB2A26273C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="3192" windowWidth="17280" windowHeight="8880" xr2:uid="{FD2C2722-0E66-47DE-A52F-2251A36C0A25}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FD2C2722-0E66-47DE-A52F-2251A36C0A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>X</t>
   </si>
@@ -138,6 +138,27 @@
   </si>
   <si>
     <t>WARDEN AVE / HUNTINGWOOD DR</t>
+  </si>
+  <si>
+    <t>THISTLETOWN COMMUNITY CENTRE</t>
+  </si>
+  <si>
+    <t>Thistletown-Beaumond Heights</t>
+  </si>
+  <si>
+    <t>ERSKINE AVE / REDPATH AVE</t>
+  </si>
+  <si>
+    <t>North Toronto</t>
+  </si>
+  <si>
+    <t>ERSKINE AVE / YOUNGE ST SMART</t>
+  </si>
+  <si>
+    <t>60 BROADWAY AVE</t>
+  </si>
+  <si>
+    <t>ROEHAMPTON AVE / MOUNT PLEASANT RD</t>
   </si>
 </sst>
 </file>
@@ -691,10 +712,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1014,17 +1031,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C89659D-35B3-4D5F-85D9-84267DD868C6}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6328125" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1044,7 +1061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>-79.375160399999999</v>
       </c>
@@ -1064,7 +1081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>-79.375106799999998</v>
       </c>
@@ -1084,7 +1101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>-79.374227000000005</v>
       </c>
@@ -1104,7 +1121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>-79.376276200000007</v>
       </c>
@@ -1124,7 +1141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>-79.375365299999999</v>
       </c>
@@ -1144,7 +1161,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>-79.373305400000007</v>
       </c>
@@ -1164,7 +1181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>-79.374217400000006</v>
       </c>
@@ -1184,7 +1201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>-79.376845900000006</v>
       </c>
@@ -1204,7 +1221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>-79.378616199999996</v>
       </c>
@@ -1224,7 +1241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>-79.378744900000001</v>
       </c>
@@ -1244,7 +1261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>-79.376717200000002</v>
       </c>
@@ -1264,7 +1281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>-79.375064899999998</v>
       </c>
@@ -1284,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>-79.376717200000002</v>
       </c>
@@ -1304,7 +1321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>-79.380257700000001</v>
       </c>
@@ -1324,7 +1341,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>-79.374808099999996</v>
       </c>
@@ -1344,7 +1361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>-79.377222099999997</v>
       </c>
@@ -1364,7 +1381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>-79.3785417</v>
       </c>
@@ -1384,7 +1401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>-79.379636099999999</v>
       </c>
@@ -1404,7 +1421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>-79.380708900000002</v>
       </c>
@@ -1424,7 +1441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>-79.376900199999994</v>
       </c>
@@ -1444,7 +1461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>-79.379056700000007</v>
       </c>
@@ -1464,7 +1481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>-79.379046000000002</v>
       </c>
@@ -1484,7 +1501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>-79.324089299999997</v>
       </c>
@@ -1504,7 +1521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>-79.316890299999997</v>
       </c>
@@ -1524,7 +1541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>-79.316106599999998</v>
       </c>
@@ -1544,7 +1561,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>-79.311342999999994</v>
       </c>
@@ -1562,24 +1579,116 @@
       </c>
       <c r="F27" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>-79.561869999999999</v>
+      </c>
+      <c r="B28" s="1">
+        <v>43.735439999999997</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>-79.394260000000003</v>
+      </c>
+      <c r="B29" s="1">
+        <v>43.712150000000001</v>
+      </c>
+      <c r="C29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="2">
+        <v>15</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>-79.398960000000002</v>
+      </c>
+      <c r="B30" s="1">
+        <v>43.711210000000001</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="2">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>-79.395740000000004</v>
+      </c>
+      <c r="B31" s="1">
+        <v>43.710259999999998</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2">
+        <v>23</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>-79.391379999999998</v>
+      </c>
+      <c r="B32" s="1">
+        <v>43.709420000000001</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="2">
+        <v>19</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CBB0E58E43B9CA4588868A803DEFF570" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e1d08d35f1bc289a16fab8295b70aa17">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ccd10a38-0784-4501-a497-12b1af63237f" xmlns:ns4="4ebc3a59-96f1-49e9-819a-e8e4fc8893ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd553773d62adc2e4d368429d5aa46e1" ns3:_="" ns4:_="">
     <xsd:import namespace="ccd10a38-0784-4501-a497-12b1af63237f"/>
@@ -1800,6 +1909,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1809,14 +1927,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B2EF9-D206-4606-8469-21E2C7BDAE17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C1E8611-BC9D-465A-AB73-E101F6DDA731}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1831,6 +1941,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B2EF9-D206-4606-8469-21E2C7BDAE17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
